--- a/Result/profitability/5498.xlsx
+++ b/Result/profitability/5498.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.01500000000000001</v>
+        <v>0.02999999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>12.62875</v>
+        <v>13.25625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-2.41</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.29375</v>
+        <v>-0.2875</v>
       </c>
       <c r="N3" t="n">
-        <v>12.025</v>
+        <v>13.12375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.29125</v>
+        <v>-0.25375</v>
       </c>
       <c r="N4" t="n">
-        <v>13.59</v>
+        <v>15.06</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3175</v>
+        <v>-0.2875</v>
       </c>
       <c r="N5" t="n">
-        <v>14.79125</v>
+        <v>15.5575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3175000000000001</v>
+        <v>-0.29625</v>
       </c>
       <c r="N6" t="n">
-        <v>15.03625</v>
+        <v>15.86625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.34</v>
+        <v>-0.3387500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>14.24625</v>
+        <v>14.49625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3575</v>
+        <v>-0.3350000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>14.32125</v>
+        <v>14.80125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.01</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01125</v>
+        <v>-0.01125000000000003</v>
       </c>
       <c r="N11" t="n">
         <v>14.11125</v>
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03000000000000001</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="N12" t="n">
         <v>13.23</v>
@@ -2028,7 +2028,7 @@
         <v>0.03</v>
       </c>
       <c r="M13" t="n">
-        <v>0.015</v>
+        <v>0.01499999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>13.395</v>
@@ -9834,6 +9834,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5498</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>583</v>
+      </c>
+      <c r="D75" t="n">
+        <v>483</v>
+      </c>
+      <c r="E75" t="n">
+        <v>100</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>50</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.65%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>59</v>
+      </c>
+      <c r="K75" t="n">
+        <v>34</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.01624999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.6475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.840000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2880720180045013</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.130000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.555253623188406</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
